--- a/task130/target/northcourt_stratification_2026_claims_draft.xlsx
+++ b/task130/target/northcourt_stratification_2026_claims_draft.xlsx
@@ -16,563 +16,6 @@
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="184">
-  <si>
-    <t>Northcourt Care Partners</t>
-  </si>
-  <si>
-    <t>Clinical Analytics</t>
-  </si>
-  <si>
-    <t>Document</t>
-  </si>
-  <si>
-    <t>Stratification of 2026 claims: DRAFT for District review</t>
-  </si>
-  <si>
-    <t>Client</t>
-  </si>
-  <si>
-    <t>Red Cedar Valley Schools Employee Health Plan (ISD 2817)</t>
-  </si>
-  <si>
-    <t>Prepared by</t>
-  </si>
-  <si>
-    <t>Amy Kelley, Clinical Analytics; Allison Santiago, Account Lead</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>14 January 2027</t>
-  </si>
-  <si>
-    <t>Data basis</t>
-  </si>
-  <si>
-    <t>Ellery medical and Quarrystone pharmacy claims incurred 1 January to 31 December 2026, paid through 31 December 2026; members enrolled on 1 January 2027</t>
-  </si>
-  <si>
-    <t>Member ID</t>
-  </si>
-  <si>
-    <t>Ellery member ID</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Northcourt Acuity Model 4.2, run on one calendar year of claims</t>
-  </si>
-  <si>
-    <t>Score</t>
-  </si>
-  <si>
-    <t>0 to 100, shown to one decimal; ranks use the unrounded score</t>
-  </si>
-  <si>
-    <t>Selection</t>
-  </si>
-  <si>
-    <t>The 140 highest-scoring members enrolled on 1 January 2027</t>
-  </si>
-  <si>
-    <t>Risk tiers</t>
-  </si>
-  <si>
-    <t>Tier 1: 53.5 and above; Tier 2: 45.5 to 53.4; Tier 3: 40.0 to 45.4; Tier 4: below 40.0</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Draft. The enrolment list will be rerun on February paid claims.</t>
-  </si>
-  <si>
-    <t>Confidential</t>
-  </si>
-  <si>
-    <t>Contains protected health information.</t>
-  </si>
-  <si>
-    <t>Rank</t>
-  </si>
-  <si>
-    <t>Relationship</t>
-  </si>
-  <si>
-    <t>Date of birth</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>Acuity score</t>
-  </si>
-  <si>
-    <t>Risk tier</t>
-  </si>
-  <si>
-    <t>RCV2162623</t>
-  </si>
-  <si>
-    <t>Subscriber</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>RCV2052974</t>
-  </si>
-  <si>
-    <t>Spouse</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>RCV2449840</t>
-  </si>
-  <si>
-    <t>RCV1471527</t>
-  </si>
-  <si>
-    <t>RCV7985309</t>
-  </si>
-  <si>
-    <t>RCV3486095</t>
-  </si>
-  <si>
-    <t>RCV4853885</t>
-  </si>
-  <si>
-    <t>RCV4984624</t>
-  </si>
-  <si>
-    <t>RCV6709117</t>
-  </si>
-  <si>
-    <t>RCV5002163</t>
-  </si>
-  <si>
-    <t>RCV8664303</t>
-  </si>
-  <si>
-    <t>RCV5033358</t>
-  </si>
-  <si>
-    <t>RCV3270069</t>
-  </si>
-  <si>
-    <t>RCV9222543</t>
-  </si>
-  <si>
-    <t>RCV8113015</t>
-  </si>
-  <si>
-    <t>Dependent</t>
-  </si>
-  <si>
-    <t>RCV2793750</t>
-  </si>
-  <si>
-    <t>RCV2071330</t>
-  </si>
-  <si>
-    <t>RCV9004175</t>
-  </si>
-  <si>
-    <t>RCV6109161</t>
-  </si>
-  <si>
-    <t>RCV3384885</t>
-  </si>
-  <si>
-    <t>RCV6942976</t>
-  </si>
-  <si>
-    <t>RCV2986773</t>
-  </si>
-  <si>
-    <t>RCV3988147</t>
-  </si>
-  <si>
-    <t>RCV4025966</t>
-  </si>
-  <si>
-    <t>RCV3675980</t>
-  </si>
-  <si>
-    <t>RCV2034883</t>
-  </si>
-  <si>
-    <t>RCV5848032</t>
-  </si>
-  <si>
-    <t>RCV6852162</t>
-  </si>
-  <si>
-    <t>RCV3257800</t>
-  </si>
-  <si>
-    <t>RCV1631184</t>
-  </si>
-  <si>
-    <t>RCV6252913</t>
-  </si>
-  <si>
-    <t>RCV3354070</t>
-  </si>
-  <si>
-    <t>RCV8201043</t>
-  </si>
-  <si>
-    <t>RCV7732575</t>
-  </si>
-  <si>
-    <t>RCV5817074</t>
-  </si>
-  <si>
-    <t>RCV4446063</t>
-  </si>
-  <si>
-    <t>RCV8039901</t>
-  </si>
-  <si>
-    <t>RCV8201650</t>
-  </si>
-  <si>
-    <t>RCV9604944</t>
-  </si>
-  <si>
-    <t>RCV7790956</t>
-  </si>
-  <si>
-    <t>RCV9720871</t>
-  </si>
-  <si>
-    <t>RCV3920778</t>
-  </si>
-  <si>
-    <t>RCV2684889</t>
-  </si>
-  <si>
-    <t>RCV3496532</t>
-  </si>
-  <si>
-    <t>RCV2337518</t>
-  </si>
-  <si>
-    <t>RCV1696191</t>
-  </si>
-  <si>
-    <t>RCV3350408</t>
-  </si>
-  <si>
-    <t>RCV9804176</t>
-  </si>
-  <si>
-    <t>RCV3674913</t>
-  </si>
-  <si>
-    <t>RCV4697258</t>
-  </si>
-  <si>
-    <t>RCV2806970</t>
-  </si>
-  <si>
-    <t>RCV1895300</t>
-  </si>
-  <si>
-    <t>RCV8017643</t>
-  </si>
-  <si>
-    <t>RCV1259489</t>
-  </si>
-  <si>
-    <t>RCV8515349</t>
-  </si>
-  <si>
-    <t>RCV4971588</t>
-  </si>
-  <si>
-    <t>RCV5561802</t>
-  </si>
-  <si>
-    <t>RCV2636159</t>
-  </si>
-  <si>
-    <t>RCV8533759</t>
-  </si>
-  <si>
-    <t>RCV2881382</t>
-  </si>
-  <si>
-    <t>RCV9611207</t>
-  </si>
-  <si>
-    <t>RCV6205499</t>
-  </si>
-  <si>
-    <t>RCV5105634</t>
-  </si>
-  <si>
-    <t>RCV1272289</t>
-  </si>
-  <si>
-    <t>RCV3504511</t>
-  </si>
-  <si>
-    <t>RCV4617151</t>
-  </si>
-  <si>
-    <t>RCV8711464</t>
-  </si>
-  <si>
-    <t>RCV1382141</t>
-  </si>
-  <si>
-    <t>RCV9942243</t>
-  </si>
-  <si>
-    <t>RCV6485110</t>
-  </si>
-  <si>
-    <t>RCV3374758</t>
-  </si>
-  <si>
-    <t>RCV3048005</t>
-  </si>
-  <si>
-    <t>RCV8955620</t>
-  </si>
-  <si>
-    <t>RCV6699713</t>
-  </si>
-  <si>
-    <t>RCV4639248</t>
-  </si>
-  <si>
-    <t>RCV5881068</t>
-  </si>
-  <si>
-    <t>RCV1609805</t>
-  </si>
-  <si>
-    <t>RCV1496883</t>
-  </si>
-  <si>
-    <t>RCV8241336</t>
-  </si>
-  <si>
-    <t>RCV4447334</t>
-  </si>
-  <si>
-    <t>RCV4679176</t>
-  </si>
-  <si>
-    <t>RCV6621103</t>
-  </si>
-  <si>
-    <t>RCV1540781</t>
-  </si>
-  <si>
-    <t>RCV4833002</t>
-  </si>
-  <si>
-    <t>RCV1411588</t>
-  </si>
-  <si>
-    <t>RCV9858043</t>
-  </si>
-  <si>
-    <t>RCV4372242</t>
-  </si>
-  <si>
-    <t>RCV2987476</t>
-  </si>
-  <si>
-    <t>RCV7620380</t>
-  </si>
-  <si>
-    <t>RCV7169467</t>
-  </si>
-  <si>
-    <t>RCV4578207</t>
-  </si>
-  <si>
-    <t>RCV4384005</t>
-  </si>
-  <si>
-    <t>RCV6463574</t>
-  </si>
-  <si>
-    <t>RCV1129734</t>
-  </si>
-  <si>
-    <t>RCV2239641</t>
-  </si>
-  <si>
-    <t>RCV7609755</t>
-  </si>
-  <si>
-    <t>RCV5670618</t>
-  </si>
-  <si>
-    <t>RCV3645671</t>
-  </si>
-  <si>
-    <t>RCV4367184</t>
-  </si>
-  <si>
-    <t>RCV2219400</t>
-  </si>
-  <si>
-    <t>RCV7784552</t>
-  </si>
-  <si>
-    <t>RCV5349249</t>
-  </si>
-  <si>
-    <t>RCV7258375</t>
-  </si>
-  <si>
-    <t>RCV7501192</t>
-  </si>
-  <si>
-    <t>RCV6298861</t>
-  </si>
-  <si>
-    <t>RCV5823710</t>
-  </si>
-  <si>
-    <t>RCV9270534</t>
-  </si>
-  <si>
-    <t>RCV6212770</t>
-  </si>
-  <si>
-    <t>RCV4087111</t>
-  </si>
-  <si>
-    <t>RCV8061593</t>
-  </si>
-  <si>
-    <t>RCV5742338</t>
-  </si>
-  <si>
-    <t>RCV1465607</t>
-  </si>
-  <si>
-    <t>RCV6179969</t>
-  </si>
-  <si>
-    <t>RCV7496703</t>
-  </si>
-  <si>
-    <t>RCV8253398</t>
-  </si>
-  <si>
-    <t>RCV4553312</t>
-  </si>
-  <si>
-    <t>RCV1033212</t>
-  </si>
-  <si>
-    <t>RCV3641827</t>
-  </si>
-  <si>
-    <t>RCV1798738</t>
-  </si>
-  <si>
-    <t>RCV8954786</t>
-  </si>
-  <si>
-    <t>RCV4353887</t>
-  </si>
-  <si>
-    <t>RCV1932981</t>
-  </si>
-  <si>
-    <t>RCV3459745</t>
-  </si>
-  <si>
-    <t>RCV8564895</t>
-  </si>
-  <si>
-    <t>RCV8440739</t>
-  </si>
-  <si>
-    <t>RCV1698430</t>
-  </si>
-  <si>
-    <t>RCV6275373</t>
-  </si>
-  <si>
-    <t>RCV8534707</t>
-  </si>
-  <si>
-    <t>RCV1692281</t>
-  </si>
-  <si>
-    <t>RCV6201973</t>
-  </si>
-  <si>
-    <t>RCV1834252</t>
-  </si>
-  <si>
-    <t>RCV6773635</t>
-  </si>
-  <si>
-    <t>RCV9354537</t>
-  </si>
-  <si>
-    <t>RCV6304613</t>
-  </si>
-  <si>
-    <t>RCV7430793</t>
-  </si>
-  <si>
-    <t>RCV6917361</t>
-  </si>
-  <si>
-    <t>RCV1573029</t>
-  </si>
-  <si>
-    <t>RCV9768130</t>
-  </si>
-  <si>
-    <t>RCV5435010</t>
-  </si>
-  <si>
-    <t>RCV4752079</t>
-  </si>
-  <si>
-    <t>Score range</t>
-  </si>
-  <si>
-    <t>Members</t>
-  </si>
-  <si>
-    <t>53.5 and above</t>
-  </si>
-  <si>
-    <t>45.5 to 53.4</t>
-  </si>
-  <si>
-    <t>40.0 to 45.4</t>
-  </si>
-  <si>
-    <t>below 40.0</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1025,99 +468,147 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Northcourt Care Partners</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Analytics</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Stratification of 2026 claims: DRAFT for District review</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Red Cedar Valley Schools Employee Health Plan (ISD 2817)</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Prepared by</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Amy Kelley, Clinical Analytics; Allison Santiago, Account Lead</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>14 January 2027</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Data basis</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ellery medical and Quarrystone pharmacy claims incurred 1 January to 31 December 2026, paid through 31 December 2026; members enrolled on 1 January 2027</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Member ID</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Ellery member ID</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Northcourt Acuity Model 4.2, run on one calendar year of claims</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>0 to 100, shown to one decimal; ranks use the unrounded score</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>The 140 highest-scoring members enrolled on 1 January 2027</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>21</v>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Risk tiers</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1: 42.2 and above; Tier 2: 37.9 to 42.1; Tier 3: 35.7 to 37.8; Tier 4: below 35.7</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>23</v>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Draft. The enrolment list will be rerun on February paid claims.</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1125,11 +616,15 @@
       <c r="B13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>25</v>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Confidential</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Contains protected health information.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1156,46 +651,66 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>31</v>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Member ID</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Date of birth</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Acuity score</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Risk tier</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RCV2730530</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>28112</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
+        <v>27163</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>63.7</v>
+        <v>65.2</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -1205,20 +720,26 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RCV2123575</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>35385</v>
-      </c>
-      <c r="E3" t="s">
-        <v>37</v>
+        <v>28572</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>63.5</v>
+        <v>56.1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1228,20 +749,26 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RCV7613430</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>30724</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
+        <v>28314</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>62.6</v>
+        <v>53.5</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1251,20 +778,26 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RCV9647098</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>29828</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
+        <v>22707</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>62.4</v>
+        <v>52.6</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1274,20 +807,26 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RCV8695211</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>25337</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
+        <v>25047</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>60.1</v>
+        <v>52.1</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1297,20 +836,26 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RCV5104636</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>24250</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
+        <v>25816</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>59.1</v>
+        <v>51.9</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -1320,20 +865,26 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RCV5999974</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>23401</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
+        <v>25712</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>58.7</v>
+        <v>50.2</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -1343,20 +894,26 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RCV8921118</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>25659</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
+        <v>29398</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>57.8</v>
+        <v>50.1</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -1366,20 +923,26 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RCV3010294</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>29468</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
+        <v>31718</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>56.9</v>
+        <v>49.8</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1389,20 +952,26 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RCV5529192</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>23650</v>
-      </c>
-      <c r="E11" t="s">
-        <v>34</v>
+        <v>23029</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>56.3</v>
+        <v>49.5</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -1412,20 +981,26 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RCV4142981</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>26578</v>
-      </c>
-      <c r="E12" t="s">
-        <v>34</v>
+        <v>25342</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>56.2</v>
+        <v>48.7</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -1435,20 +1010,26 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RCV6367920</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>22013</v>
-      </c>
-      <c r="E13" t="s">
-        <v>37</v>
+        <v>24140</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>55.8</v>
+        <v>47.8</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -1458,20 +1039,26 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RCV3449444</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>28481</v>
-      </c>
-      <c r="E14" t="s">
-        <v>34</v>
+        <v>26580</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>55.7</v>
+        <v>47.2</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -1481,20 +1068,26 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RCV5035018</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>21246</v>
-      </c>
-      <c r="E15" t="s">
-        <v>34</v>
+        <v>38557</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>55.7</v>
+        <v>46.7</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1504,20 +1097,26 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RCV6528985</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>46141</v>
-      </c>
-      <c r="E16" t="s">
-        <v>37</v>
+        <v>25730</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>55.5</v>
+        <v>46.6</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1527,20 +1126,26 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" t="s">
-        <v>36</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>RCV5816729</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>28514</v>
-      </c>
-      <c r="E17" t="s">
-        <v>37</v>
+        <v>26908</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>55</v>
+        <v>46.4</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1550,20 +1155,26 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" t="s">
-        <v>33</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RCV4660775</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>36138</v>
-      </c>
-      <c r="E18" t="s">
-        <v>34</v>
+        <v>27309</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>54.9</v>
+        <v>46.1</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1573,20 +1184,26 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" t="s">
-        <v>33</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RCV1135609</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>27709</v>
-      </c>
-      <c r="E19" t="s">
-        <v>34</v>
+        <v>23369</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>54.2</v>
+        <v>46.1</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -1596,20 +1213,26 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" t="s">
-        <v>33</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>RCV8355110</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>33797</v>
-      </c>
-      <c r="E20" t="s">
-        <v>37</v>
+        <v>22295</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>53.8</v>
+        <v>45.9</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1619,365 +1242,461 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" t="s">
-        <v>36</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RCV9467205</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>22733</v>
-      </c>
-      <c r="E21" t="s">
-        <v>37</v>
+        <v>24582</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>53.4</v>
+        <v>45.7</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" t="s">
-        <v>36</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RCV7885533</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>21946</v>
-      </c>
-      <c r="E22" t="s">
-        <v>37</v>
+        <v>26975</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>53.1</v>
+        <v>45.4</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" t="s">
-        <v>36</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>RCV1603872</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>29539</v>
-      </c>
-      <c r="E23" t="s">
-        <v>37</v>
+        <v>35090</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>52.6</v>
+        <v>45.3</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" t="s">
-        <v>36</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RCV6227172</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>28221</v>
-      </c>
-      <c r="E24" t="s">
-        <v>34</v>
+        <v>42371</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" t="s">
-        <v>33</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>RCV9255613</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>36686</v>
-      </c>
-      <c r="E25" t="s">
-        <v>34</v>
+        <v>26377</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>52.4</v>
+        <v>44.7</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" t="s">
-        <v>33</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RCV4189407</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>27942</v>
-      </c>
-      <c r="E26" t="s">
-        <v>37</v>
+        <v>29800</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>52.3</v>
+        <v>44.7</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" t="s">
-        <v>36</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RCV3082787</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>23571</v>
-      </c>
-      <c r="E27" t="s">
-        <v>37</v>
+        <v>27148</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>51.8</v>
+        <v>43.7</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" t="s">
-        <v>36</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RCV5995844</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>25399</v>
-      </c>
-      <c r="E28" t="s">
-        <v>37</v>
+        <v>21605</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>51.6</v>
+        <v>43.7</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RCV2751065</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>23158</v>
-      </c>
-      <c r="E29" t="s">
-        <v>34</v>
+        <v>24692</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>51.5</v>
+        <v>43.7</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" t="s">
-        <v>33</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>RCV4587185</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>27357</v>
-      </c>
-      <c r="E30" t="s">
-        <v>37</v>
+        <v>24894</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F30" s="6" t="n">
-        <v>51.2</v>
+        <v>43.5</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>66</v>
-      </c>
-      <c r="C31" t="s">
-        <v>33</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>RCV9304806</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>26740</v>
-      </c>
-      <c r="E31" t="s">
-        <v>34</v>
+        <v>24622</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>50.7</v>
+        <v>43</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" t="s">
-        <v>36</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RCV8608275</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>33488</v>
-      </c>
-      <c r="E32" t="s">
-        <v>34</v>
+        <v>31641</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>50.3</v>
+        <v>43</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" t="s">
-        <v>51</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RCV8509472</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>46224</v>
-      </c>
-      <c r="E33" t="s">
-        <v>37</v>
+        <v>27468</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>50.1</v>
+        <v>42.7</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" t="s">
-        <v>36</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>RCV7157512</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>27792</v>
-      </c>
-      <c r="E34" t="s">
-        <v>37</v>
+        <v>23754</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F34" s="6" t="n">
-        <v>50.1</v>
+        <v>42.6</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" t="s">
-        <v>51</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>RCV6938522</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>39361</v>
-      </c>
-      <c r="E35" t="s">
-        <v>34</v>
+        <v>25222</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>50</v>
+        <v>42.3</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" t="s">
-        <v>36</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RCV4201512</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>23290</v>
-      </c>
-      <c r="E36" t="s">
-        <v>37</v>
+        <v>29300</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>49.2</v>
+        <v>41.9</v>
       </c>
       <c r="G36" t="n">
         <v>2</v>
@@ -1987,20 +1706,26 @@
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" t="s">
-        <v>36</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>RCV3713263</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>26490</v>
-      </c>
-      <c r="E37" t="s">
-        <v>34</v>
+        <v>29087</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>49.2</v>
+        <v>41.4</v>
       </c>
       <c r="G37" t="n">
         <v>2</v>
@@ -2010,20 +1735,26 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" t="s">
-        <v>33</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>RCV5579448</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>23303</v>
-      </c>
-      <c r="E38" t="s">
-        <v>34</v>
+        <v>25764</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>49</v>
+        <v>41.3</v>
       </c>
       <c r="G38" t="n">
         <v>2</v>
@@ -2033,20 +1764,26 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" t="s">
-        <v>36</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RCV1855123</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>24021</v>
-      </c>
-      <c r="E39" t="s">
-        <v>34</v>
+        <v>32038</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>48.5</v>
+        <v>41</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
@@ -2056,20 +1793,26 @@
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" t="s">
-        <v>33</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>RCV5181969</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>26073</v>
-      </c>
-      <c r="E40" t="s">
-        <v>34</v>
+        <v>23566</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>48.4</v>
+        <v>40.9</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
@@ -2079,20 +1822,26 @@
       <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" t="s">
-        <v>33</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RCV5078746</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>29081</v>
-      </c>
-      <c r="E41" t="s">
-        <v>37</v>
+        <v>28655</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>48.3</v>
+        <v>40.9</v>
       </c>
       <c r="G41" t="n">
         <v>2</v>
@@ -2102,20 +1851,26 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>77</v>
-      </c>
-      <c r="C42" t="s">
-        <v>51</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>RCV5824630</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>43864</v>
-      </c>
-      <c r="E42" t="s">
-        <v>37</v>
+        <v>28492</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>47.9</v>
+        <v>40.8</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
@@ -2125,20 +1880,26 @@
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" t="s">
-        <v>33</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>RCV1070060</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>28013</v>
-      </c>
-      <c r="E43" t="s">
-        <v>34</v>
+        <v>30349</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>47.7</v>
+        <v>40.8</v>
       </c>
       <c r="G43" t="n">
         <v>2</v>
@@ -2148,20 +1909,26 @@
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" t="s">
-        <v>33</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RCV2327923</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>23830</v>
-      </c>
-      <c r="E44" t="s">
-        <v>34</v>
+        <v>25183</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>47.6</v>
+        <v>40.7</v>
       </c>
       <c r="G44" t="n">
         <v>2</v>
@@ -2171,20 +1938,26 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" t="s">
-        <v>33</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>RCV6875151</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>34028</v>
-      </c>
-      <c r="E45" t="s">
-        <v>34</v>
+        <v>40112</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>47.2</v>
+        <v>40.6</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
@@ -2194,20 +1967,26 @@
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
-        <v>81</v>
-      </c>
-      <c r="C46" t="s">
-        <v>36</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RCV2365593</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>23339</v>
-      </c>
-      <c r="E46" t="s">
-        <v>37</v>
+        <v>33612</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>46.7</v>
+        <v>40.4</v>
       </c>
       <c r="G46" t="n">
         <v>2</v>
@@ -2217,20 +1996,26 @@
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
-        <v>82</v>
-      </c>
-      <c r="C47" t="s">
-        <v>33</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>RCV3282444</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>23537</v>
-      </c>
-      <c r="E47" t="s">
-        <v>34</v>
+        <v>34034</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>46.6</v>
+        <v>40.1</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
@@ -2240,20 +2025,26 @@
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>83</v>
-      </c>
-      <c r="C48" t="s">
-        <v>33</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>RCV8050854</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>24902</v>
-      </c>
-      <c r="E48" t="s">
-        <v>37</v>
+        <v>24862</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>46.5</v>
+        <v>39.9</v>
       </c>
       <c r="G48" t="n">
         <v>2</v>
@@ -2263,20 +2054,26 @@
       <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
-        <v>84</v>
-      </c>
-      <c r="C49" t="s">
-        <v>33</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>RCV2919565</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>23900</v>
-      </c>
-      <c r="E49" t="s">
-        <v>34</v>
+        <v>24306</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>46.2</v>
+        <v>39.6</v>
       </c>
       <c r="G49" t="n">
         <v>2</v>
@@ -2286,20 +2083,26 @@
       <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" t="s">
-        <v>33</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RCV8852933</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>30286</v>
-      </c>
-      <c r="E50" t="s">
-        <v>34</v>
+        <v>26254</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>46.1</v>
+        <v>39.6</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
@@ -2309,20 +2112,26 @@
       <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
-        <v>86</v>
-      </c>
-      <c r="C51" t="s">
-        <v>33</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RCV5510200</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>29706</v>
-      </c>
-      <c r="E51" t="s">
-        <v>37</v>
+        <v>28439</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>45.9</v>
+        <v>39.3</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
@@ -2332,20 +2141,26 @@
       <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
-        <v>87</v>
-      </c>
-      <c r="C52" t="s">
-        <v>36</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RCV6795042</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>26312</v>
-      </c>
-      <c r="E52" t="s">
-        <v>37</v>
+        <v>23652</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>45.6</v>
+        <v>39.2</v>
       </c>
       <c r="G52" t="n">
         <v>2</v>
@@ -2355,20 +2170,26 @@
       <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" t="s">
-        <v>33</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>RCV5566499</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>26225</v>
-      </c>
-      <c r="E53" t="s">
-        <v>34</v>
+        <v>46134</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>45.5</v>
+        <v>39.2</v>
       </c>
       <c r="G53" t="n">
         <v>2</v>
@@ -2378,411 +2199,519 @@
       <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
-        <v>89</v>
-      </c>
-      <c r="C54" t="s">
-        <v>33</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>RCV4899050</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>26541</v>
-      </c>
-      <c r="E54" t="s">
-        <v>34</v>
+        <v>24208</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>45.4</v>
+        <v>39.1</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
-        <v>90</v>
-      </c>
-      <c r="C55" t="s">
-        <v>33</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RCV1947586</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>23356</v>
-      </c>
-      <c r="E55" t="s">
-        <v>34</v>
+        <v>35326</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F55" s="6" t="n">
-        <v>45.2</v>
+        <v>39.1</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
-        <v>91</v>
-      </c>
-      <c r="C56" t="s">
-        <v>51</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RCV5863375</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>44818</v>
-      </c>
-      <c r="E56" t="s">
-        <v>34</v>
+        <v>20965</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>45.1</v>
+        <v>39</v>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" t="s">
-        <v>51</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RCV1203862</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>46271</v>
-      </c>
-      <c r="E57" t="s">
-        <v>37</v>
+        <v>30841</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" t="s">
-        <v>36</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RCV5168987</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>23333</v>
-      </c>
-      <c r="E58" t="s">
-        <v>34</v>
+        <v>33637</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>44.7</v>
+        <v>38.9</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" t="s">
-        <v>33</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>RCV8834952</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>23611</v>
-      </c>
-      <c r="E59" t="s">
-        <v>34</v>
+        <v>35129</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>44.6</v>
+        <v>38.7</v>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
-        <v>95</v>
-      </c>
-      <c r="C60" t="s">
-        <v>33</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>RCV2810335</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>34426</v>
-      </c>
-      <c r="E60" t="s">
-        <v>34</v>
+        <v>25295</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F60" s="6" t="n">
-        <v>44.4</v>
+        <v>38.6</v>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
-        <v>96</v>
-      </c>
-      <c r="C61" t="s">
-        <v>36</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>RCV7668760</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>33649</v>
-      </c>
-      <c r="E61" t="s">
-        <v>37</v>
+        <v>37190</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>44.4</v>
+        <v>38.5</v>
       </c>
       <c r="G61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
-        <v>97</v>
-      </c>
-      <c r="C62" t="s">
-        <v>33</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>RCV9968668</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>25360</v>
-      </c>
-      <c r="E62" t="s">
-        <v>37</v>
+        <v>32548</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>44.4</v>
+        <v>38.4</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
-        <v>98</v>
-      </c>
-      <c r="C63" t="s">
-        <v>33</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>RCV6032188</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>30791</v>
-      </c>
-      <c r="E63" t="s">
-        <v>37</v>
+        <v>30936</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>44.3</v>
+        <v>38.4</v>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
-        <v>99</v>
-      </c>
-      <c r="C64" t="s">
-        <v>33</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>RCV1657905</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>32960</v>
-      </c>
-      <c r="E64" t="s">
-        <v>37</v>
+        <v>30867</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F64" s="6" t="n">
-        <v>44.2</v>
+        <v>38.3</v>
       </c>
       <c r="G64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
-        <v>100</v>
-      </c>
-      <c r="C65" t="s">
-        <v>33</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>RCV3942326</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>31451</v>
-      </c>
-      <c r="E65" t="s">
-        <v>34</v>
+        <v>27790</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F65" s="6" t="n">
-        <v>44.1</v>
+        <v>38.2</v>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
-        <v>101</v>
-      </c>
-      <c r="C66" t="s">
-        <v>36</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RCV1049263</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>30131</v>
-      </c>
-      <c r="E66" t="s">
-        <v>34</v>
+        <v>32024</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F66" s="6" t="n">
-        <v>44.1</v>
+        <v>38.1</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
-        <v>102</v>
-      </c>
-      <c r="C67" t="s">
-        <v>36</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>RCV1315676</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>28485</v>
-      </c>
-      <c r="E67" t="s">
-        <v>37</v>
+        <v>27786</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F67" s="6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
-        <v>103</v>
-      </c>
-      <c r="C68" t="s">
-        <v>33</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RCV5283668</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>23337</v>
-      </c>
-      <c r="E68" t="s">
-        <v>37</v>
+        <v>28947</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F68" s="6" t="n">
-        <v>43.7</v>
+        <v>38</v>
       </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
-        <v>104</v>
-      </c>
-      <c r="C69" t="s">
-        <v>33</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RCV4533275</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>26857</v>
-      </c>
-      <c r="E69" t="s">
-        <v>37</v>
+        <v>46224</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F69" s="6" t="n">
-        <v>43.6</v>
+        <v>38</v>
       </c>
       <c r="G69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
-        <v>105</v>
-      </c>
-      <c r="C70" t="s">
-        <v>36</v>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>RCV9495454</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>28330</v>
-      </c>
-      <c r="E70" t="s">
-        <v>34</v>
+        <v>28824</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F70" s="6" t="n">
-        <v>43.5</v>
+        <v>37.9</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
-        <v>106</v>
-      </c>
-      <c r="C71" t="s">
-        <v>36</v>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>RCV5315428</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>25130</v>
-      </c>
-      <c r="E71" t="s">
-        <v>37</v>
+        <v>30154</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F71" s="6" t="n">
-        <v>43.4</v>
+        <v>37.8</v>
       </c>
       <c r="G71" t="n">
         <v>3</v>
@@ -2792,20 +2721,26 @@
       <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
-        <v>107</v>
-      </c>
-      <c r="C72" t="s">
-        <v>33</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>RCV2409617</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>28246</v>
-      </c>
-      <c r="E72" t="s">
-        <v>37</v>
+        <v>28877</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F72" s="6" t="n">
-        <v>43.3</v>
+        <v>37.7</v>
       </c>
       <c r="G72" t="n">
         <v>3</v>
@@ -2815,20 +2750,26 @@
       <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
-        <v>108</v>
-      </c>
-      <c r="C73" t="s">
-        <v>33</v>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>RCV2960214</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>31905</v>
-      </c>
-      <c r="E73" t="s">
-        <v>34</v>
+        <v>27298</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F73" s="6" t="n">
-        <v>43.2</v>
+        <v>37.7</v>
       </c>
       <c r="G73" t="n">
         <v>3</v>
@@ -2838,20 +2779,26 @@
       <c r="A74" t="n">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
-        <v>109</v>
-      </c>
-      <c r="C74" t="s">
-        <v>33</v>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>RCV4210913</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>26708</v>
-      </c>
-      <c r="E74" t="s">
-        <v>37</v>
+        <v>37516</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F74" s="6" t="n">
-        <v>43.1</v>
+        <v>37.5</v>
       </c>
       <c r="G74" t="n">
         <v>3</v>
@@ -2861,20 +2808,26 @@
       <c r="A75" t="n">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
-        <v>110</v>
-      </c>
-      <c r="C75" t="s">
-        <v>33</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>RCV1277465</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>29632</v>
-      </c>
-      <c r="E75" t="s">
-        <v>34</v>
+        <v>27961</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F75" s="6" t="n">
-        <v>42.8</v>
+        <v>37.3</v>
       </c>
       <c r="G75" t="n">
         <v>3</v>
@@ -2884,20 +2837,26 @@
       <c r="A76" t="n">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
-        <v>111</v>
-      </c>
-      <c r="C76" t="s">
-        <v>33</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>RCV7862809</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>28765</v>
-      </c>
-      <c r="E76" t="s">
-        <v>34</v>
+        <v>31271</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>42.1</v>
+        <v>37.1</v>
       </c>
       <c r="G76" t="n">
         <v>3</v>
@@ -2907,20 +2866,26 @@
       <c r="A77" t="n">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
-        <v>112</v>
-      </c>
-      <c r="C77" t="s">
-        <v>33</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>RCV5591867</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>24183</v>
-      </c>
-      <c r="E77" t="s">
-        <v>34</v>
+        <v>27813</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F77" s="6" t="n">
-        <v>42.1</v>
+        <v>37.1</v>
       </c>
       <c r="G77" t="n">
         <v>3</v>
@@ -2930,20 +2895,26 @@
       <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
-        <v>113</v>
-      </c>
-      <c r="C78" t="s">
-        <v>36</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>RCV8014223</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>24947</v>
-      </c>
-      <c r="E78" t="s">
-        <v>37</v>
+        <v>27902</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F78" s="6" t="n">
-        <v>42.1</v>
+        <v>37.1</v>
       </c>
       <c r="G78" t="n">
         <v>3</v>
@@ -2953,20 +2924,26 @@
       <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
-        <v>114</v>
-      </c>
-      <c r="C79" t="s">
-        <v>36</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>RCV9437872</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>26702</v>
-      </c>
-      <c r="E79" t="s">
-        <v>37</v>
+        <v>29427</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F79" s="6" t="n">
-        <v>42</v>
+        <v>37.1</v>
       </c>
       <c r="G79" t="n">
         <v>3</v>
@@ -2976,20 +2953,26 @@
       <c r="A80" t="n">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
-        <v>115</v>
-      </c>
-      <c r="C80" t="s">
-        <v>36</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>RCV4467829</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>25180</v>
-      </c>
-      <c r="E80" t="s">
+        <v>37122</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="n">
         <v>37</v>
-      </c>
-      <c r="F80" s="6" t="n">
-        <v>42</v>
       </c>
       <c r="G80" t="n">
         <v>3</v>
@@ -2999,20 +2982,26 @@
       <c r="A81" t="n">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
-        <v>116</v>
-      </c>
-      <c r="C81" t="s">
-        <v>33</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RCV5279940</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>23171</v>
-      </c>
-      <c r="E81" t="s">
-        <v>37</v>
+        <v>23734</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F81" s="6" t="n">
-        <v>41.9</v>
+        <v>36.9</v>
       </c>
       <c r="G81" t="n">
         <v>3</v>
@@ -3022,20 +3011,26 @@
       <c r="A82" t="n">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
-        <v>117</v>
-      </c>
-      <c r="C82" t="s">
-        <v>33</v>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>RCV9952179</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>23903</v>
-      </c>
-      <c r="E82" t="s">
-        <v>34</v>
+        <v>26412</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F82" s="6" t="n">
-        <v>41.8</v>
+        <v>36.8</v>
       </c>
       <c r="G82" t="n">
         <v>3</v>
@@ -3045,20 +3040,26 @@
       <c r="A83" t="n">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
-        <v>118</v>
-      </c>
-      <c r="C83" t="s">
-        <v>33</v>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>RCV1937360</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>31499</v>
-      </c>
-      <c r="E83" t="s">
-        <v>34</v>
+        <v>33054</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F83" s="6" t="n">
-        <v>41.8</v>
+        <v>36.8</v>
       </c>
       <c r="G83" t="n">
         <v>3</v>
@@ -3068,20 +3069,26 @@
       <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
-        <v>119</v>
-      </c>
-      <c r="C84" t="s">
-        <v>33</v>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>RCV2975871</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>31691</v>
-      </c>
-      <c r="E84" t="s">
-        <v>37</v>
+        <v>29352</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F84" s="6" t="n">
-        <v>41.7</v>
+        <v>36.8</v>
       </c>
       <c r="G84" t="n">
         <v>3</v>
@@ -3091,20 +3098,26 @@
       <c r="A85" t="n">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
-        <v>120</v>
-      </c>
-      <c r="C85" t="s">
-        <v>36</v>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>RCV8621093</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>24113</v>
-      </c>
-      <c r="E85" t="s">
-        <v>37</v>
+        <v>31277</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F85" s="6" t="n">
-        <v>41.6</v>
+        <v>36.6</v>
       </c>
       <c r="G85" t="n">
         <v>3</v>
@@ -3114,20 +3127,26 @@
       <c r="A86" t="n">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
-        <v>121</v>
-      </c>
-      <c r="C86" t="s">
-        <v>33</v>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>RCV6197369</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>23801</v>
-      </c>
-      <c r="E86" t="s">
-        <v>34</v>
+        <v>35840</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F86" s="6" t="n">
-        <v>41.3</v>
+        <v>36.6</v>
       </c>
       <c r="G86" t="n">
         <v>3</v>
@@ -3137,20 +3156,26 @@
       <c r="A87" t="n">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
-        <v>122</v>
-      </c>
-      <c r="C87" t="s">
-        <v>33</v>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>RCV1523489</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>33777</v>
-      </c>
-      <c r="E87" t="s">
-        <v>34</v>
+        <v>24655</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F87" s="6" t="n">
-        <v>41.3</v>
+        <v>36.5</v>
       </c>
       <c r="G87" t="n">
         <v>3</v>
@@ -3160,20 +3185,26 @@
       <c r="A88" t="n">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
-        <v>123</v>
-      </c>
-      <c r="C88" t="s">
-        <v>36</v>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>RCV5746488</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>33615</v>
-      </c>
-      <c r="E88" t="s">
-        <v>34</v>
+        <v>46315</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F88" s="6" t="n">
-        <v>41.2</v>
+        <v>36.3</v>
       </c>
       <c r="G88" t="n">
         <v>3</v>
@@ -3183,20 +3214,26 @@
       <c r="A89" t="n">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
-        <v>124</v>
-      </c>
-      <c r="C89" t="s">
-        <v>51</v>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>RCV6769341</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>40371</v>
-      </c>
-      <c r="E89" t="s">
-        <v>37</v>
+        <v>24072</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F89" s="6" t="n">
-        <v>40.9</v>
+        <v>36.2</v>
       </c>
       <c r="G89" t="n">
         <v>3</v>
@@ -3206,20 +3243,26 @@
       <c r="A90" t="n">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
-        <v>125</v>
-      </c>
-      <c r="C90" t="s">
-        <v>33</v>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>RCV7304462</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>30584</v>
-      </c>
-      <c r="E90" t="s">
-        <v>37</v>
+        <v>25208</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F90" s="6" t="n">
-        <v>40.9</v>
+        <v>36.2</v>
       </c>
       <c r="G90" t="n">
         <v>3</v>
@@ -3229,20 +3272,26 @@
       <c r="A91" t="n">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
-        <v>126</v>
-      </c>
-      <c r="C91" t="s">
-        <v>33</v>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>RCV2632014</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>23163</v>
-      </c>
-      <c r="E91" t="s">
-        <v>37</v>
+        <v>23907</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F91" s="6" t="n">
-        <v>40.9</v>
+        <v>36.2</v>
       </c>
       <c r="G91" t="n">
         <v>3</v>
@@ -3252,20 +3301,26 @@
       <c r="A92" t="n">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
-        <v>127</v>
-      </c>
-      <c r="C92" t="s">
-        <v>33</v>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>RCV3217981</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>23210</v>
-      </c>
-      <c r="E92" t="s">
-        <v>37</v>
+        <v>28198</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F92" s="6" t="n">
-        <v>40.8</v>
+        <v>36.2</v>
       </c>
       <c r="G92" t="n">
         <v>3</v>
@@ -3275,20 +3330,26 @@
       <c r="A93" t="n">
         <v>92</v>
       </c>
-      <c r="B93" t="s">
-        <v>128</v>
-      </c>
-      <c r="C93" t="s">
-        <v>33</v>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>RCV5710113</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>24564</v>
-      </c>
-      <c r="E93" t="s">
-        <v>34</v>
+        <v>26352</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F93" s="6" t="n">
-        <v>40.7</v>
+        <v>36.2</v>
       </c>
       <c r="G93" t="n">
         <v>3</v>
@@ -3298,20 +3359,26 @@
       <c r="A94" t="n">
         <v>93</v>
       </c>
-      <c r="B94" t="s">
-        <v>129</v>
-      </c>
-      <c r="C94" t="s">
-        <v>36</v>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>RCV2747077</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D94" s="5" t="n">
-        <v>29070</v>
-      </c>
-      <c r="E94" t="s">
-        <v>37</v>
+        <v>28998</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F94" s="6" t="n">
-        <v>40.6</v>
+        <v>36.1</v>
       </c>
       <c r="G94" t="n">
         <v>3</v>
@@ -3321,20 +3388,26 @@
       <c r="A95" t="n">
         <v>94</v>
       </c>
-      <c r="B95" t="s">
-        <v>130</v>
-      </c>
-      <c r="C95" t="s">
-        <v>36</v>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>RCV6190692</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>29158</v>
-      </c>
-      <c r="E95" t="s">
-        <v>34</v>
+        <v>30533</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F95" s="6" t="n">
-        <v>40.5</v>
+        <v>36.1</v>
       </c>
       <c r="G95" t="n">
         <v>3</v>
@@ -3344,20 +3417,26 @@
       <c r="A96" t="n">
         <v>95</v>
       </c>
-      <c r="B96" t="s">
-        <v>131</v>
-      </c>
-      <c r="C96" t="s">
-        <v>51</v>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>RCV9766459</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>46084</v>
-      </c>
-      <c r="E96" t="s">
-        <v>34</v>
+        <v>24804</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F96" s="6" t="n">
-        <v>40.3</v>
+        <v>36</v>
       </c>
       <c r="G96" t="n">
         <v>3</v>
@@ -3367,20 +3446,26 @@
       <c r="A97" t="n">
         <v>96</v>
       </c>
-      <c r="B97" t="s">
-        <v>132</v>
-      </c>
-      <c r="C97" t="s">
-        <v>51</v>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>RCV4869334</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>44701</v>
-      </c>
-      <c r="E97" t="s">
-        <v>37</v>
+        <v>26404</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F97" s="6" t="n">
-        <v>40.2</v>
+        <v>35.9</v>
       </c>
       <c r="G97" t="n">
         <v>3</v>
@@ -3390,20 +3475,26 @@
       <c r="A98" t="n">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
-        <v>133</v>
-      </c>
-      <c r="C98" t="s">
-        <v>36</v>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>RCV9121410</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>28315</v>
-      </c>
-      <c r="E98" t="s">
-        <v>34</v>
+        <v>28952</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F98" s="6" t="n">
-        <v>40</v>
+        <v>35.9</v>
       </c>
       <c r="G98" t="n">
         <v>3</v>
@@ -3413,135 +3504,171 @@
       <c r="A99" t="n">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
-        <v>134</v>
-      </c>
-      <c r="C99" t="s">
-        <v>33</v>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>RCV1071872</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>33343</v>
-      </c>
-      <c r="E99" t="s">
-        <v>34</v>
+        <v>26578</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F99" s="6" t="n">
-        <v>39.8</v>
+        <v>35.8</v>
       </c>
       <c r="G99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
-        <v>135</v>
-      </c>
-      <c r="C100" t="s">
-        <v>33</v>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>RCV1913391</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>27481</v>
-      </c>
-      <c r="E100" t="s">
-        <v>34</v>
+        <v>27834</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F100" s="6" t="n">
-        <v>39.7</v>
+        <v>35.8</v>
       </c>
       <c r="G100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
-        <v>136</v>
-      </c>
-      <c r="C101" t="s">
-        <v>33</v>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>RCV5515162</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>24814</v>
-      </c>
-      <c r="E101" t="s">
-        <v>34</v>
+        <v>24710</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F101" s="6" t="n">
-        <v>39.7</v>
+        <v>35.7</v>
       </c>
       <c r="G101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
-        <v>137</v>
-      </c>
-      <c r="C102" t="s">
-        <v>33</v>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>RCV2747974</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>36884</v>
-      </c>
-      <c r="E102" t="s">
-        <v>37</v>
+        <v>23888</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F102" s="6" t="n">
-        <v>39.7</v>
+        <v>35.7</v>
       </c>
       <c r="G102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
-        <v>138</v>
-      </c>
-      <c r="C103" t="s">
-        <v>51</v>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>RCV6796246</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>44507</v>
-      </c>
-      <c r="E103" t="s">
-        <v>37</v>
+        <v>37581</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F103" s="6" t="n">
-        <v>39.6</v>
+        <v>35.7</v>
       </c>
       <c r="G103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
-        <v>139</v>
-      </c>
-      <c r="C104" t="s">
-        <v>33</v>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>RCV8318861</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>23803</v>
-      </c>
-      <c r="E104" t="s">
-        <v>37</v>
+        <v>24802</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F104" s="6" t="n">
-        <v>39.6</v>
+        <v>35.5</v>
       </c>
       <c r="G104" t="n">
         <v>4</v>
@@ -3551,20 +3678,26 @@
       <c r="A105" t="n">
         <v>104</v>
       </c>
-      <c r="B105" t="s">
-        <v>140</v>
-      </c>
-      <c r="C105" t="s">
-        <v>36</v>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>RCV5346787</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>31225</v>
-      </c>
-      <c r="E105" t="s">
-        <v>34</v>
+        <v>24109</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F105" s="6" t="n">
-        <v>39.4</v>
+        <v>35.5</v>
       </c>
       <c r="G105" t="n">
         <v>4</v>
@@ -3574,20 +3707,26 @@
       <c r="A106" t="n">
         <v>105</v>
       </c>
-      <c r="B106" t="s">
-        <v>141</v>
-      </c>
-      <c r="C106" t="s">
-        <v>33</v>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>RCV6528527</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>23249</v>
-      </c>
-      <c r="E106" t="s">
-        <v>34</v>
+        <v>23942</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F106" s="6" t="n">
-        <v>39.4</v>
+        <v>35.5</v>
       </c>
       <c r="G106" t="n">
         <v>4</v>
@@ -3597,20 +3736,26 @@
       <c r="A107" t="n">
         <v>106</v>
       </c>
-      <c r="B107" t="s">
-        <v>142</v>
-      </c>
-      <c r="C107" t="s">
-        <v>51</v>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>RCV2283246</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>44577</v>
-      </c>
-      <c r="E107" t="s">
-        <v>37</v>
+        <v>25235</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F107" s="6" t="n">
-        <v>39.4</v>
+        <v>35.4</v>
       </c>
       <c r="G107" t="n">
         <v>4</v>
@@ -3620,20 +3765,26 @@
       <c r="A108" t="n">
         <v>107</v>
       </c>
-      <c r="B108" t="s">
-        <v>143</v>
-      </c>
-      <c r="C108" t="s">
-        <v>33</v>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>RCV5380081</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>33357</v>
-      </c>
-      <c r="E108" t="s">
-        <v>34</v>
+        <v>30367</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F108" s="6" t="n">
-        <v>39.1</v>
+        <v>35.3</v>
       </c>
       <c r="G108" t="n">
         <v>4</v>
@@ -3643,20 +3794,26 @@
       <c r="A109" t="n">
         <v>108</v>
       </c>
-      <c r="B109" t="s">
-        <v>144</v>
-      </c>
-      <c r="C109" t="s">
-        <v>33</v>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>RCV7845029</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>32346</v>
-      </c>
-      <c r="E109" t="s">
-        <v>37</v>
+        <v>26342</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F109" s="6" t="n">
-        <v>39.1</v>
+        <v>35.3</v>
       </c>
       <c r="G109" t="n">
         <v>4</v>
@@ -3666,20 +3823,26 @@
       <c r="A110" t="n">
         <v>109</v>
       </c>
-      <c r="B110" t="s">
-        <v>145</v>
-      </c>
-      <c r="C110" t="s">
-        <v>33</v>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>RCV9761816</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D110" s="5" t="n">
-        <v>27193</v>
-      </c>
-      <c r="E110" t="s">
-        <v>37</v>
+        <v>33923</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F110" s="6" t="n">
-        <v>39</v>
+        <v>35.3</v>
       </c>
       <c r="G110" t="n">
         <v>4</v>
@@ -3689,20 +3852,26 @@
       <c r="A111" t="n">
         <v>110</v>
       </c>
-      <c r="B111" t="s">
-        <v>146</v>
-      </c>
-      <c r="C111" t="s">
-        <v>51</v>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>RCV3189078</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>43880</v>
-      </c>
-      <c r="E111" t="s">
-        <v>37</v>
+        <v>26567</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F111" s="6" t="n">
-        <v>38.9</v>
+        <v>35.2</v>
       </c>
       <c r="G111" t="n">
         <v>4</v>
@@ -3712,20 +3881,26 @@
       <c r="A112" t="n">
         <v>111</v>
       </c>
-      <c r="B112" t="s">
-        <v>147</v>
-      </c>
-      <c r="C112" t="s">
-        <v>51</v>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>RCV4756035</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>42862</v>
-      </c>
-      <c r="E112" t="s">
-        <v>37</v>
+        <v>32179</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F112" s="6" t="n">
-        <v>38.8</v>
+        <v>35.2</v>
       </c>
       <c r="G112" t="n">
         <v>4</v>
@@ -3735,20 +3910,26 @@
       <c r="A113" t="n">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
-        <v>148</v>
-      </c>
-      <c r="C113" t="s">
-        <v>36</v>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RCV1123220</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>28732</v>
-      </c>
-      <c r="E113" t="s">
-        <v>37</v>
+        <v>40929</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F113" s="6" t="n">
-        <v>38.8</v>
+        <v>35.2</v>
       </c>
       <c r="G113" t="n">
         <v>4</v>
@@ -3758,20 +3939,26 @@
       <c r="A114" t="n">
         <v>113</v>
       </c>
-      <c r="B114" t="s">
-        <v>149</v>
-      </c>
-      <c r="C114" t="s">
-        <v>33</v>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>RCV5202951</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>25840</v>
-      </c>
-      <c r="E114" t="s">
-        <v>34</v>
+        <v>26983</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F114" s="6" t="n">
-        <v>38.8</v>
+        <v>35.2</v>
       </c>
       <c r="G114" t="n">
         <v>4</v>
@@ -3781,20 +3968,26 @@
       <c r="A115" t="n">
         <v>114</v>
       </c>
-      <c r="B115" t="s">
-        <v>150</v>
-      </c>
-      <c r="C115" t="s">
-        <v>33</v>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>RCV4711403</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>30219</v>
-      </c>
-      <c r="E115" t="s">
-        <v>34</v>
+        <v>30268</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F115" s="6" t="n">
-        <v>38.5</v>
+        <v>35.2</v>
       </c>
       <c r="G115" t="n">
         <v>4</v>
@@ -3804,20 +3997,26 @@
       <c r="A116" t="n">
         <v>115</v>
       </c>
-      <c r="B116" t="s">
-        <v>151</v>
-      </c>
-      <c r="C116" t="s">
-        <v>33</v>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RCV5866544</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D116" s="5" t="n">
-        <v>32281</v>
-      </c>
-      <c r="E116" t="s">
-        <v>34</v>
+        <v>26442</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F116" s="6" t="n">
-        <v>38.5</v>
+        <v>35</v>
       </c>
       <c r="G116" t="n">
         <v>4</v>
@@ -3827,20 +4026,26 @@
       <c r="A117" t="n">
         <v>116</v>
       </c>
-      <c r="B117" t="s">
-        <v>152</v>
-      </c>
-      <c r="C117" t="s">
-        <v>51</v>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>RCV9596296</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>42192</v>
-      </c>
-      <c r="E117" t="s">
-        <v>34</v>
+        <v>35110</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F117" s="6" t="n">
-        <v>38.4</v>
+        <v>34.9</v>
       </c>
       <c r="G117" t="n">
         <v>4</v>
@@ -3850,20 +4055,26 @@
       <c r="A118" t="n">
         <v>117</v>
       </c>
-      <c r="B118" t="s">
-        <v>153</v>
-      </c>
-      <c r="C118" t="s">
-        <v>51</v>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>RCV3651381</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>40654</v>
-      </c>
-      <c r="E118" t="s">
-        <v>34</v>
+        <v>22917</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F118" s="6" t="n">
-        <v>38.3</v>
+        <v>34.7</v>
       </c>
       <c r="G118" t="n">
         <v>4</v>
@@ -3873,20 +4084,26 @@
       <c r="A119" t="n">
         <v>118</v>
       </c>
-      <c r="B119" t="s">
-        <v>154</v>
-      </c>
-      <c r="C119" t="s">
-        <v>33</v>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>RCV7948468</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>30656</v>
-      </c>
-      <c r="E119" t="s">
-        <v>34</v>
+        <v>30313</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F119" s="6" t="n">
-        <v>38.3</v>
+        <v>34.7</v>
       </c>
       <c r="G119" t="n">
         <v>4</v>
@@ -3896,20 +4113,26 @@
       <c r="A120" t="n">
         <v>119</v>
       </c>
-      <c r="B120" t="s">
-        <v>155</v>
-      </c>
-      <c r="C120" t="s">
-        <v>33</v>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>RCV2102741</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>26701</v>
-      </c>
-      <c r="E120" t="s">
-        <v>37</v>
+        <v>24658</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F120" s="6" t="n">
-        <v>38.3</v>
+        <v>34.7</v>
       </c>
       <c r="G120" t="n">
         <v>4</v>
@@ -3919,20 +4142,26 @@
       <c r="A121" t="n">
         <v>120</v>
       </c>
-      <c r="B121" t="s">
-        <v>156</v>
-      </c>
-      <c r="C121" t="s">
-        <v>33</v>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>RCV7028261</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>37179</v>
-      </c>
-      <c r="E121" t="s">
-        <v>34</v>
+        <v>33353</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F121" s="6" t="n">
-        <v>38.3</v>
+        <v>34.7</v>
       </c>
       <c r="G121" t="n">
         <v>4</v>
@@ -3942,20 +4171,26 @@
       <c r="A122" t="n">
         <v>121</v>
       </c>
-      <c r="B122" t="s">
-        <v>157</v>
-      </c>
-      <c r="C122" t="s">
-        <v>33</v>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>RCV8733567</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>26858</v>
-      </c>
-      <c r="E122" t="s">
-        <v>37</v>
+        <v>29775</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F122" s="6" t="n">
-        <v>38.2</v>
+        <v>34.6</v>
       </c>
       <c r="G122" t="n">
         <v>4</v>
@@ -3965,20 +4200,26 @@
       <c r="A123" t="n">
         <v>122</v>
       </c>
-      <c r="B123" t="s">
-        <v>158</v>
-      </c>
-      <c r="C123" t="s">
-        <v>33</v>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>RCV1589842</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>24876</v>
-      </c>
-      <c r="E123" t="s">
-        <v>34</v>
+        <v>25677</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F123" s="6" t="n">
-        <v>38.1</v>
+        <v>34.6</v>
       </c>
       <c r="G123" t="n">
         <v>4</v>
@@ -3988,20 +4229,26 @@
       <c r="A124" t="n">
         <v>123</v>
       </c>
-      <c r="B124" t="s">
-        <v>159</v>
-      </c>
-      <c r="C124" t="s">
-        <v>36</v>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>RCV4985729</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>23956</v>
-      </c>
-      <c r="E124" t="s">
-        <v>37</v>
+        <v>27802</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F124" s="6" t="n">
-        <v>38</v>
+        <v>34.5</v>
       </c>
       <c r="G124" t="n">
         <v>4</v>
@@ -4011,20 +4258,26 @@
       <c r="A125" t="n">
         <v>124</v>
       </c>
-      <c r="B125" t="s">
-        <v>160</v>
-      </c>
-      <c r="C125" t="s">
-        <v>36</v>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>RCV4477427</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>22804</v>
-      </c>
-      <c r="E125" t="s">
-        <v>34</v>
+        <v>26813</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F125" s="6" t="n">
-        <v>37.9</v>
+        <v>34.5</v>
       </c>
       <c r="G125" t="n">
         <v>4</v>
@@ -4034,20 +4287,26 @@
       <c r="A126" t="n">
         <v>125</v>
       </c>
-      <c r="B126" t="s">
-        <v>161</v>
-      </c>
-      <c r="C126" t="s">
-        <v>33</v>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>RCV8057849</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D126" s="5" t="n">
-        <v>23473</v>
-      </c>
-      <c r="E126" t="s">
-        <v>34</v>
+        <v>25491</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F126" s="6" t="n">
-        <v>37.9</v>
+        <v>34.4</v>
       </c>
       <c r="G126" t="n">
         <v>4</v>
@@ -4057,20 +4316,26 @@
       <c r="A127" t="n">
         <v>126</v>
       </c>
-      <c r="B127" t="s">
-        <v>162</v>
-      </c>
-      <c r="C127" t="s">
-        <v>51</v>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>RCV8843842</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>46292</v>
-      </c>
-      <c r="E127" t="s">
-        <v>37</v>
+        <v>39518</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F127" s="6" t="n">
-        <v>37.9</v>
+        <v>34.4</v>
       </c>
       <c r="G127" t="n">
         <v>4</v>
@@ -4080,20 +4345,26 @@
       <c r="A128" t="n">
         <v>127</v>
       </c>
-      <c r="B128" t="s">
-        <v>163</v>
-      </c>
-      <c r="C128" t="s">
-        <v>36</v>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>RCV4314756</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D128" s="5" t="n">
-        <v>30220</v>
-      </c>
-      <c r="E128" t="s">
-        <v>37</v>
+        <v>30552</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F128" s="6" t="n">
-        <v>37.8</v>
+        <v>34.4</v>
       </c>
       <c r="G128" t="n">
         <v>4</v>
@@ -4103,20 +4374,26 @@
       <c r="A129" t="n">
         <v>128</v>
       </c>
-      <c r="B129" t="s">
-        <v>164</v>
-      </c>
-      <c r="C129" t="s">
-        <v>36</v>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>RCV4504310</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>25295</v>
-      </c>
-      <c r="E129" t="s">
-        <v>37</v>
+        <v>25850</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F129" s="6" t="n">
-        <v>37.8</v>
+        <v>34.2</v>
       </c>
       <c r="G129" t="n">
         <v>4</v>
@@ -4126,20 +4403,26 @@
       <c r="A130" t="n">
         <v>129</v>
       </c>
-      <c r="B130" t="s">
-        <v>165</v>
-      </c>
-      <c r="C130" t="s">
-        <v>33</v>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>RCV7151567</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D130" s="5" t="n">
-        <v>27341</v>
-      </c>
-      <c r="E130" t="s">
-        <v>37</v>
+        <v>35540</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F130" s="6" t="n">
-        <v>37.8</v>
+        <v>34.2</v>
       </c>
       <c r="G130" t="n">
         <v>4</v>
@@ -4149,20 +4432,26 @@
       <c r="A131" t="n">
         <v>130</v>
       </c>
-      <c r="B131" t="s">
-        <v>166</v>
-      </c>
-      <c r="C131" t="s">
-        <v>33</v>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RCV8277482</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>23896</v>
-      </c>
-      <c r="E131" t="s">
-        <v>37</v>
+        <v>36580</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F131" s="6" t="n">
-        <v>37.7</v>
+        <v>34.1</v>
       </c>
       <c r="G131" t="n">
         <v>4</v>
@@ -4172,20 +4461,26 @@
       <c r="A132" t="n">
         <v>131</v>
       </c>
-      <c r="B132" t="s">
-        <v>167</v>
-      </c>
-      <c r="C132" t="s">
-        <v>33</v>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>RCV9058604</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D132" s="5" t="n">
-        <v>24187</v>
-      </c>
-      <c r="E132" t="s">
-        <v>37</v>
+        <v>31045</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F132" s="6" t="n">
-        <v>37.7</v>
+        <v>34.1</v>
       </c>
       <c r="G132" t="n">
         <v>4</v>
@@ -4195,20 +4490,26 @@
       <c r="A133" t="n">
         <v>132</v>
       </c>
-      <c r="B133" t="s">
-        <v>168</v>
-      </c>
-      <c r="C133" t="s">
-        <v>36</v>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>RCV9033976</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>27850</v>
-      </c>
-      <c r="E133" t="s">
-        <v>37</v>
+        <v>28598</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F133" s="6" t="n">
-        <v>37.5</v>
+        <v>34.1</v>
       </c>
       <c r="G133" t="n">
         <v>4</v>
@@ -4218,20 +4519,26 @@
       <c r="A134" t="n">
         <v>133</v>
       </c>
-      <c r="B134" t="s">
-        <v>169</v>
-      </c>
-      <c r="C134" t="s">
-        <v>33</v>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>RCV4268380</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Dependent</t>
+        </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>23964</v>
-      </c>
-      <c r="E134" t="s">
-        <v>37</v>
+        <v>46273</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
       </c>
       <c r="F134" s="6" t="n">
-        <v>37.4</v>
+        <v>34.1</v>
       </c>
       <c r="G134" t="n">
         <v>4</v>
@@ -4241,20 +4548,26 @@
       <c r="A135" t="n">
         <v>134</v>
       </c>
-      <c r="B135" t="s">
-        <v>170</v>
-      </c>
-      <c r="C135" t="s">
-        <v>36</v>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>RCV9870490</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>27956</v>
-      </c>
-      <c r="E135" t="s">
-        <v>37</v>
+        <v>24564</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F135" s="6" t="n">
-        <v>37.4</v>
+        <v>34.1</v>
       </c>
       <c r="G135" t="n">
         <v>4</v>
@@ -4264,20 +4577,26 @@
       <c r="A136" t="n">
         <v>135</v>
       </c>
-      <c r="B136" t="s">
-        <v>171</v>
-      </c>
-      <c r="C136" t="s">
-        <v>36</v>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>RCV8139215</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D136" s="5" t="n">
-        <v>28704</v>
-      </c>
-      <c r="E136" t="s">
-        <v>37</v>
+        <v>22913</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F136" s="6" t="n">
-        <v>37.2</v>
+        <v>34.1</v>
       </c>
       <c r="G136" t="n">
         <v>4</v>
@@ -4287,20 +4606,26 @@
       <c r="A137" t="n">
         <v>136</v>
       </c>
-      <c r="B137" t="s">
-        <v>172</v>
-      </c>
-      <c r="C137" t="s">
-        <v>33</v>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>RCV8996300</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>33730</v>
-      </c>
-      <c r="E137" t="s">
+        <v>23265</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="n">
         <v>34</v>
-      </c>
-      <c r="F137" s="6" t="n">
-        <v>37.2</v>
       </c>
       <c r="G137" t="n">
         <v>4</v>
@@ -4310,20 +4635,26 @@
       <c r="A138" t="n">
         <v>137</v>
       </c>
-      <c r="B138" t="s">
-        <v>173</v>
-      </c>
-      <c r="C138" t="s">
-        <v>36</v>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RCV5137035</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>24222</v>
-      </c>
-      <c r="E138" t="s">
-        <v>37</v>
+        <v>34208</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F138" s="6" t="n">
-        <v>37.1</v>
+        <v>34</v>
       </c>
       <c r="G138" t="n">
         <v>4</v>
@@ -4333,20 +4664,26 @@
       <c r="A139" t="n">
         <v>138</v>
       </c>
-      <c r="B139" t="s">
-        <v>174</v>
-      </c>
-      <c r="C139" t="s">
-        <v>51</v>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RCV7511334</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>46161</v>
-      </c>
-      <c r="E139" t="s">
-        <v>37</v>
+        <v>26328</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F139" s="6" t="n">
-        <v>37.1</v>
+        <v>34</v>
       </c>
       <c r="G139" t="n">
         <v>4</v>
@@ -4356,20 +4693,26 @@
       <c r="A140" t="n">
         <v>139</v>
       </c>
-      <c r="B140" t="s">
-        <v>175</v>
-      </c>
-      <c r="C140" t="s">
-        <v>33</v>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>RCV8655465</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D140" s="5" t="n">
-        <v>30595</v>
-      </c>
-      <c r="E140" t="s">
+        <v>21010</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="n">
         <v>34</v>
-      </c>
-      <c r="F140" s="6" t="n">
-        <v>37.1</v>
       </c>
       <c r="G140" t="n">
         <v>4</v>
@@ -4379,20 +4722,26 @@
       <c r="A141" t="n">
         <v>140</v>
       </c>
-      <c r="B141" t="s">
-        <v>176</v>
-      </c>
-      <c r="C141" t="s">
-        <v>36</v>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>RCV8167445</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Subscriber</t>
+        </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>29361</v>
-      </c>
-      <c r="E141" t="s">
-        <v>37</v>
+        <v>24016</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
       </c>
       <c r="F141" s="6" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G141" t="n">
         <v>4</v>
@@ -4419,63 +4768,79 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>178</v>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Risk tier</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Score range</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Members</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>179</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>42.2 and above</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>180</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>37.9 to 42.1</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>181</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>35.7 to 37.8</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>182</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>below 35.7</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>183</v>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
       <c r="C6" s="8" t="n">
         <v>140</v>
